--- a/output/pdf_financials_xlsx/ICON.xlsx
+++ b/output/pdf_financials_xlsx/ICON.xlsx
@@ -1102,22 +1102,22 @@
         <v>-2.0203</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.429381</v>
+        <v>-0.429381</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.435831</v>
+        <v>-0.435831</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.581815</v>
+        <v>-1.581815</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.618446</v>
+        <v>-1.618446</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.664951</v>
+        <v>-0.664951</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.937032</v>
+        <v>-1.937032</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-1.463213</v>
@@ -1338,22 +1338,22 @@
         <v>-2.0203</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.429381</v>
+        <v>-0.429381</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.435831</v>
+        <v>-0.435831</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1.581815</v>
+        <v>-1.581815</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.618446</v>
+        <v>-1.618446</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.664951</v>
+        <v>-0.664951</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.937032</v>
+        <v>-1.937032</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-1.463213</v>
@@ -1476,22 +1476,22 @@
         <v>-2.0203</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.429381</v>
+        <v>-0.429381</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.435831</v>
+        <v>-0.435831</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.581815</v>
+        <v>-1.581815</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.618446</v>
+        <v>-1.618446</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.664951</v>
+        <v>-0.664951</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.937032</v>
+        <v>-1.937032</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-1.463213</v>
@@ -1632,10 +1632,10 @@
         <v>101.015</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-10.734525</v>
+        <v>10.734525</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-14.5277</v>
+        <v>14.5277</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -1688,22 +1688,22 @@
         <v>-2.0203</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.429381</v>
+        <v>-0.429381</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.435831</v>
+        <v>-0.435831</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.581815</v>
+        <v>-1.581815</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.618446</v>
+        <v>-1.618446</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.664951</v>
+        <v>-0.664951</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.937032</v>
+        <v>-1.937032</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-1.463213</v>
@@ -1780,22 +1780,22 @@
         <v>-2.020144</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.429923</v>
+        <v>-0.428839</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.436109</v>
+        <v>-0.435553</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.581815</v>
+        <v>-1.581815</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.618446</v>
+        <v>-1.618446</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.664951</v>
+        <v>-0.664951</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.937032</v>
+        <v>-1.937032</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-1.463213</v>
@@ -1898,22 +1898,22 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-0</v>
@@ -36789,10 +36789,10 @@
         </is>
       </c>
       <c r="M376" s="5" t="n">
-        <v>1.937032</v>
+        <v>-1.937032</v>
       </c>
       <c r="N376" s="5" t="n">
-        <v>1.463213</v>
+        <v>-1.463213</v>
       </c>
       <c r="O376" t="inlineStr">
         <is>
@@ -38884,10 +38884,10 @@
         </is>
       </c>
       <c r="L402" s="5" t="n">
-        <v>0.664951</v>
+        <v>-0.664951</v>
       </c>
       <c r="M402" s="5" t="n">
-        <v>1.937032</v>
+        <v>-1.937032</v>
       </c>
       <c r="N402" t="inlineStr">
         <is>
@@ -40297,10 +40297,10 @@
         </is>
       </c>
       <c r="K420" s="5" t="n">
-        <v>1.618446</v>
+        <v>-1.618446</v>
       </c>
       <c r="L420" s="5" t="n">
-        <v>0.664951</v>
+        <v>-0.664951</v>
       </c>
       <c r="M420" t="inlineStr">
         <is>
@@ -42045,7 +42045,7 @@
         </is>
       </c>
       <c r="I442" s="5" t="n">
-        <v>0.435831</v>
+        <v>-0.435831</v>
       </c>
       <c r="J442" s="5" t="n">
         <v>1.581815</v>
@@ -45021,10 +45021,10 @@
         <v>-2.0203</v>
       </c>
       <c r="H479" s="5" t="n">
-        <v>0.429381</v>
+        <v>-0.429381</v>
       </c>
       <c r="I479" s="5" t="n">
-        <v>0.435831</v>
+        <v>-0.435831</v>
       </c>
       <c r="J479" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ICON.xlsx
+++ b/output/pdf_financials_xlsx/ICON.xlsx
@@ -939,13 +939,13 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.022517</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.362856</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.36492</v>
       </c>
     </row>
     <row r="13">
@@ -1709,13 +1709,13 @@
         <v>-1.463213</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>7.196613</v>
+        <v>7.174096</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.7460639999999999</v>
+        <v>-1.10892</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-7.825643</v>
+        <v>-8.190562999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1801,13 +1801,13 @@
         <v>-1.463213</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>7.196613</v>
+        <v>7.174096</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.7460639999999999</v>
+        <v>-1.10892</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-7.825643</v>
+        <v>-8.190562999999999</v>
       </c>
     </row>
     <row r="30">
@@ -2026,31 +2026,31 @@
         <v>0.023388</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.033487</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.24612</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.026296</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.054562</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.05745</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.05745</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.019144</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.003504</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.021246</v>
       </c>
     </row>
     <row r="35">
@@ -2118,31 +2118,31 @@
         <v>0.023388</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.033487</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.24612</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.026296</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.054562</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.05745</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.05745</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.019144</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.003504</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.021246</v>
       </c>
     </row>
     <row r="37">
@@ -2670,31 +2670,31 @@
         <v>0.006037</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.053334</v>
+        <v>0.019847</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.286091</v>
+        <v>0.039971</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.026296</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.069369</v>
+        <v>0.014807</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.204746</v>
+        <v>0.147296</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.204746</v>
+        <v>0.147296</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.08348</v>
+        <v>0.064336</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>3.448041</v>
+        <v>3.444537</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.022466</v>
+        <v>0.00122</v>
       </c>
     </row>
     <row r="49">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -31674,7 +31674,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -33511,7 +33511,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">

--- a/output/pdf_financials_xlsx/ICON.xlsx
+++ b/output/pdf_financials_xlsx/ICON.xlsx
@@ -679,13 +679,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.475056</v>
+        <v>0.507724</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.096332</v>
+        <v>0.131306</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.089396</v>
+        <v>0.129396</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.475056</v>
+        <v>0.507724</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.096332</v>
+        <v>0.131306</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.089396</v>
+        <v>0.129396</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
@@ -869,7 +869,7 @@
         <v>-0.329697</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.089396</v>
+        <v>-0.129396</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.055954</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.07480199999999999</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.113539</v>
       </c>
       <c r="E67" s="3" t="n">
         <v>0</v>
@@ -5560,16 +5560,16 @@
         <v>0</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.001281</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.036896</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.203651</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.116162</v>
       </c>
       <c r="M110" s="3" t="n">
         <v>0</v>
@@ -18816,7 +18816,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -19288,7 +19292,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -23132,7 +23140,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -28146,7 +28158,11 @@
           <t>Shares issued for cash 9</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -29600,7 +29616,11 @@
           <t>GST Receivable</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -29837,7 +29857,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E290" s="5" t="n">
         <v>0.95</v>
       </c>
@@ -45490,7 +45514,11 @@
           <t>Director fees (Note 10)</t>
         </is>
       </c>
-      <c r="D485" t="inlineStr"/>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E485" t="inlineStr">
         <is>
           <t>-</t>
@@ -46551,7 +46579,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E498" s="5" t="n">
         <v>0.032668</v>
       </c>
